--- a/Excel/Lab 1/Lab 1.xlsx
+++ b/Excel/Lab 1/Lab 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\newHDD\Data Analysis using Excel-Ahmed Ismail\ITI Tasks\Final Assessment-Excel analysis\Labs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF22653-B79E-4C0E-860B-9E05E899E8C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AFB715-D4F2-437A-82FB-EC0EEB5FAEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{6E0772BF-1D0C-417B-A4B2-B12690A11A9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23760" windowHeight="15840" xr2:uid="{6E0772BF-1D0C-417B-A4B2-B12690A11A9F}"/>
   </bookViews>
   <sheets>
     <sheet name="EX1" sheetId="1" r:id="rId1"/>
@@ -731,10 +731,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
@@ -746,7 +743,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -942,7 +942,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Orders"/>
@@ -12452,9 +12452,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -12492,7 +12492,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -12598,7 +12598,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -12740,7 +12740,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -12751,7 +12751,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" style="4" bestFit="1" customWidth="1"/>
@@ -13170,7 +13170,7 @@
       <c r="E16" s="31"/>
       <c r="M16" s="33"/>
     </row>
-    <row r="17" spans="2:10" ht="15.75" thickBot="1">
+    <row r="17" spans="2:7" ht="15.75" thickBot="1">
       <c r="B17" s="3"/>
       <c r="C17" s="29" t="s">
         <v>55</v>
@@ -13179,166 +13179,110 @@
       <c r="E17" s="31"/>
       <c r="G17" s="34"/>
     </row>
-    <row r="18" spans="2:10" ht="15.75" thickBot="1">
+    <row r="18" spans="2:7" ht="15.75" thickBot="1">
       <c r="C18" s="29" t="s">
         <v>56</v>
       </c>
       <c r="D18" s="30"/>
       <c r="E18" s="31"/>
     </row>
-    <row r="19" spans="2:10" ht="15.75" thickBot="1">
+    <row r="19" spans="2:7" ht="15.75" thickBot="1">
       <c r="C19" s="29" t="s">
         <v>35</v>
       </c>
       <c r="D19" s="30"/>
       <c r="E19" s="31"/>
     </row>
-    <row r="20" spans="2:10" ht="15.75" thickBot="1">
+    <row r="20" spans="2:7" ht="15.75" thickBot="1">
       <c r="C20" s="29" t="s">
         <v>37</v>
       </c>
       <c r="D20" s="30"/>
       <c r="E20" s="31"/>
     </row>
-    <row r="21" spans="2:10" ht="14.25" customHeight="1" thickBot="1">
+    <row r="21" spans="2:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="C21" s="35" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="36"/>
       <c r="E21" s="37"/>
     </row>
-    <row r="22" spans="2:10" ht="15.75" thickBot="1">
+    <row r="22" spans="2:7" ht="15.75" thickBot="1">
       <c r="C22" s="35" t="s">
         <v>41</v>
       </c>
       <c r="D22" s="36"/>
       <c r="E22" s="37"/>
-      <c r="I22" s="28">
-        <v>10</v>
-      </c>
-      <c r="J22" s="4">
-        <v>4</v>
-      </c>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:7">
       <c r="C23" s="35" t="s">
         <v>43</v>
       </c>
       <c r="D23" s="36"/>
       <c r="E23" s="37"/>
-      <c r="I23" s="28">
-        <v>15</v>
-      </c>
-      <c r="J23" s="4">
-        <v>3</v>
-      </c>
     </row>
-    <row r="24" spans="2:10">
-      <c r="I24" s="28">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10">
-      <c r="I25" s="28">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" ht="23.25">
-      <c r="C26" s="49" t="s">
+    <row r="26" spans="2:7" ht="23.25">
+      <c r="C26" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="I26" s="28">
-        <v>2</v>
-      </c>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
     </row>
-    <row r="27" spans="2:10">
-      <c r="I27" s="28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" ht="18.75">
-      <c r="C28" s="54" t="s">
+    <row r="28" spans="2:7" ht="18.75">
+      <c r="C28" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="51"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="53"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="52"/>
     </row>
-    <row r="29" spans="2:10" ht="18.75">
-      <c r="C29" s="54" t="s">
+    <row r="29" spans="2:7" ht="18.75">
+      <c r="C29" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="51"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="53"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="52"/>
     </row>
-    <row r="30" spans="2:10" ht="18.75">
-      <c r="C30" s="54" t="s">
+    <row r="30" spans="2:7" ht="18.75">
+      <c r="C30" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="51"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="53"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52"/>
     </row>
-    <row r="31" spans="2:10" ht="18.75">
-      <c r="C31" s="54" t="s">
+    <row r="31" spans="2:7" ht="18.75">
+      <c r="C31" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="D31" s="51"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="53"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="52"/>
     </row>
-    <row r="32" spans="2:10" ht="18.75">
-      <c r="C32" s="54" t="s">
+    <row r="32" spans="2:7" ht="18.75">
+      <c r="C32" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="51"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="53"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="52"/>
     </row>
-    <row r="33" spans="3:9" ht="18.75">
-      <c r="C33" s="54" t="s">
+    <row r="33" spans="3:6" ht="18.75">
+      <c r="C33" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="D33" s="51"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="53"/>
-      <c r="I33" s="28">
-        <v>30</v>
-      </c>
+      <c r="D33" s="50"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="52"/>
     </row>
-    <row r="34" spans="3:9">
-      <c r="I34" s="28">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="3:9">
-      <c r="I35" s="28">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="3:9">
+    <row r="36" spans="3:6">
       <c r="F36" s="38"/>
-      <c r="I36" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="3:9">
-      <c r="I37" s="28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="3:9">
-      <c r="I38" s="28">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
-  <sortState ref="I33:I38">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I33:I38">
     <sortCondition descending="1" ref="I33"/>
   </sortState>
   <mergeCells count="7">
